--- a/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260706104452</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-07-06T10:44:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -181,12 +181,6 @@
   </si>
   <si>
     <t>présence +++ sur +++</t>
-  </si>
-  <si>
-    <t>373121007</t>
-  </si>
-  <si>
-    <t>test non effectué</t>
   </si>
   <si>
     <t/>
@@ -459,7 +453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -591,23 +585,15 @@
         <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>58</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260706104452</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T10:44:52+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
